--- a/upload/links2026.xlsx
+++ b/upload/links2026.xlsx
@@ -6678,6 +6678,7 @@
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
